--- a/dcf/TECK.xlsx
+++ b/dcf/TECK.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.08478000973207547</v>
+        <v>0.08451967424435206</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.08978000973207548</v>
+        <v>0.08951967424435206</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.09478000973207547</v>
+        <v>0.09451967424435205</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.09978000973207547</v>
+        <v>0.09951967424435205</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1047800097320755</v>
+        <v>0.1045196742443521</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1097800097320755</v>
+        <v>0.109519674244352</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1147800097320755</v>
+        <v>0.1145196742443521</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>21.64827747472309</v>
+        <v>21.70080143908082</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>20.66499800323884</v>
+        <v>20.71502001097178</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>19.72841966634835</v>
+        <v>19.77607223839608</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>18.8360750227035</v>
+        <v>18.88148306080393</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>17.98563815778854</v>
+        <v>18.02891941523532</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>17.1749159599387</v>
+        <v>17.21618148128158</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>16.40183997058836</v>
+        <v>16.44119450245265</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>23.90683115491922</v>
+        <v>23.96478256553418</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>22.82204088783432</v>
+        <v>22.87722259137905</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>21.78894787288881</v>
+        <v>21.84150673537907</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>20.80481761643432</v>
+        <v>20.85489205579631</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>19.86707254686092</v>
+        <v>19.91479305503866</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>18.97328233906622</v>
+        <v>19.01877196967857</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>18.1211548758906</v>
+        <v>18.16452969985223</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>26.16538483511534</v>
+        <v>26.22876369198754</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>24.9790837724298</v>
+        <v>25.03942517178631</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>23.84947607942929</v>
+        <v>23.90694123236206</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>22.77356021016515</v>
+        <v>22.82830105078869</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>21.74850693593331</v>
+        <v>21.80066669484199</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>20.77164871819374</v>
+        <v>20.82136245807556</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>19.84046978119284</v>
+        <v>19.88786489725181</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>28.42393851531148</v>
+        <v>28.49274481844091</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>27.13612665702529</v>
+        <v>27.20162775219358</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>25.91000428596976</v>
+        <v>25.97237572934505</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>24.74230280389597</v>
+        <v>24.80171004578107</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>23.6299413250057</v>
+        <v>23.68654033464533</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>22.57001509732126</v>
+        <v>22.62395294647255</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>21.55978468649509</v>
+        <v>21.6112000946514</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>30.68249219550761</v>
+        <v>30.75672594489427</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>29.29316954162078</v>
+        <v>29.36383033260084</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>27.97053249251023</v>
+        <v>28.03781022632803</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>26.7110453976268</v>
+        <v>26.77511904077345</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>25.51137571407808</v>
+        <v>25.57241397444867</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>24.36838147644878</v>
+        <v>24.42654343486954</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>23.27909959179733</v>
+        <v>23.33453529205099</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>32.94104587570374</v>
+        <v>33.02070707134764</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>31.45021242621626</v>
+        <v>31.5260329130081</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>30.03106069905071</v>
+        <v>30.10324472331103</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>28.67978799135763</v>
+        <v>28.74852803576583</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>27.39281010315046</v>
+        <v>27.458287614252</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>26.16674785557631</v>
+        <v>26.22913392326652</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>24.99841449709958</v>
+        <v>25.05787048945057</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>35.19959955589987</v>
+        <v>35.284688197801</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>33.60725531081175</v>
+        <v>33.68823549341538</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>32.09158890559118</v>
+        <v>32.16867922029402</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>30.64853058508846</v>
+        <v>30.72193703075821</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>29.27424449222285</v>
+        <v>29.34416125405534</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>27.96511423470383</v>
+        <v>28.03172441166352</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>26.71772940240183</v>
+        <v>26.78120568685016</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>60.0099983215332</v>
+        <v>58.95000076293945</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.09978000973207547</v>
+        <v>0.09951967424435205</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.6855143943910452</v>
+        <v>0.6855312168514404</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>60.0099983215332</v>
+        <v>58.95000076293945</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>24.74230280389597</v>
+        <v>24.80171004578107</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>38.45675607576264</v>
+        <v>38.54582889415378</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>14.36341819112576</v>
+        <v>14.4007701475533</v>
       </c>
     </row>
     <row r="59">
